--- a/Sufficient data WITH_PO/forecast_summary_B0BZQ416QM_WITH_PO.xlsx
+++ b/Sufficient data WITH_PO/forecast_summary_B0BZQ416QM_WITH_PO.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.03</v>
+        <v>0.99</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.09</v>
+        <v>0.98</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.02</v>
+        <v>0.98</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0.86</v>
+        <v>0.9</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>72</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
     </row>
